--- a/output/reporte_h2_2025.xlsx
+++ b/output/reporte_h2_2025.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4969</v>
+        <v>2996</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6430</v>
+        <v>3873</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7727838258164852</v>
+        <v>0.7735605473792926</v>
       </c>
     </row>
     <row r="9">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5003</v>
+        <v>4548</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5389</v>
+        <v>4873</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9283726108740026</v>
+        <v>0.9333059716806895</v>
       </c>
     </row>
     <row r="11">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1307</v>
+        <v>880</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1925</v>
+        <v>1181</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.678961038961039</v>
+        <v>0.7451312447078747</v>
       </c>
     </row>
     <row r="12">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>28984</v>
+        <v>26062</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32916</v>
+        <v>29472</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8805444160894398</v>
+        <v>0.8842969598262758</v>
       </c>
     </row>
     <row r="15">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6932</v>
+        <v>3537</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8788</v>
+        <v>4402</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7888029130632681</v>
+        <v>0.803498409813721</v>
       </c>
     </row>
     <row r="17">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>974</v>
+        <v>215</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1495</v>
+        <v>249</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.651505016722408</v>
+        <v>0.8634538152610441</v>
       </c>
     </row>
     <row r="12">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3995</v>
+        <v>2781</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4935</v>
+        <v>3624</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7673841059602649</v>
       </c>
     </row>
     <row r="13">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1088</v>
+        <v>633</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1195</v>
+        <v>679</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9104602510460251</v>
+        <v>0.9322533136966127</v>
       </c>
     </row>
     <row r="15">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1307</v>
+        <v>880</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1925</v>
+        <v>1181</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.678961038961039</v>
+        <v>0.7451312447078747</v>
       </c>
     </row>
     <row r="18">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5735</v>
+        <v>2813</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6382</v>
+        <v>2938</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8986211219053588</v>
+        <v>0.9574540503744043</v>
       </c>
     </row>
     <row r="25">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3396</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4387</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7741053111465694</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2508,13 +2508,13 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>760</v>
+        <v>215</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>826</v>
+        <v>248</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.9200968523002422</v>
+        <v>0.8669354838709677</v>
       </c>
     </row>
     <row r="42">
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2551,38 +2551,38 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0</v>
+        <v>2781</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1</v>
+        <v>3624</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0</v>
+        <v>0.7673841059602649</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -2598,17 +2598,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -2624,336 +2624,336 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>653</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3124042879019908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>72</v>
+        <v>1737</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>103</v>
+        <v>2125</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.6990291262135923</v>
+        <v>0.8174117647058824</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1</v>
+        <v>792</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>7</v>
+        <v>957</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.8275862068965517</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>156</v>
+        <v>736</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>163</v>
+        <v>791</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.9570552147239264</v>
+        <v>0.9304677623261695</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.8441558441558441</v>
+        <v>0.8809523809523809</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>37</v>
+        <v>666</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>38</v>
+        <v>725</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9186206896551724</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>4</v>
+        <v>633</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>4</v>
+        <v>679</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1</v>
+        <v>0.9322533136966127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2781</v>
+        <v>1</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>3624</v>
+        <v>6</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.7673841059602649</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>1</v>
@@ -2962,24 +2962,24 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>1</v>
@@ -2988,2163 +2988,1305 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>868</v>
+        <v>2654</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>906</v>
+        <v>2739</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.9580573951434879</v>
+        <v>0.9689667761956918</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0</v>
+        <v>1255</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2</v>
+        <v>1443</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0</v>
+        <v>0.8697158697158697</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7903225806451613</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7058823529411765</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2</v>
+        <v>994</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
+        <v>0.727364185110664</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1737</v>
+        <v>161</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2125</v>
+        <v>174</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>0.8174117647058824</v>
+        <v>0.9252873563218391</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>792</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>957</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>736</v>
+        <v>685</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>791</v>
+        <v>732</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.9304677623261695</v>
+        <v>0.9357923497267759</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.851063829787234</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>666</v>
+        <v>47</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>725</v>
+        <v>59</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.9186206896551724</v>
+        <v>0.7966101694915254</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>208</v>
+        <v>1946</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>238</v>
+        <v>2062</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0.8739495798319328</v>
+        <v>0.9437439379243453</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>757</v>
+        <v>3</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.9220607661822986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>182</v>
+        <v>1153</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>199</v>
+        <v>1437</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.914572864321608</v>
+        <v>0.802366040361865</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>0</v>
+        <v>0.6574074074074074</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1</v>
+        <v>3307</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1</v>
+        <v>3615</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1</v>
+        <v>0.9147994467496542</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>3</v>
+        <v>2197</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>3</v>
+        <v>2305</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1</v>
+        <v>0.9531453362255965</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2654</v>
+        <v>2764</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2739</v>
+        <v>3028</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9689667761956918</v>
+        <v>0.9128137384412153</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1255</v>
+        <v>1</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1443</v>
+        <v>2</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8697158697158697</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1</v>
+        <v>3774</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2</v>
+        <v>4480</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8424107142857142</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>64</v>
+        <v>2296</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>70</v>
+        <v>2621</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.876001526135063</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F84" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>11</v>
+        <v>1281</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>16</v>
+        <v>1484</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>0.6875</v>
+        <v>0.8632075471698113</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.95</v>
+        <v>0.8387096774193549</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>32</v>
+        <v>1983</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>38</v>
+        <v>2072</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.957046332046332</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>49</v>
+        <v>547</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>62</v>
+        <v>825</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.6630303030303031</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>12</v>
+        <v>2559</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>17</v>
+        <v>2814</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.9093816631130064</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>1119</v>
+        <v>2813</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1700</v>
+        <v>2938</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.658235294117647</v>
+        <v>0.9574540503744043</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>161</v>
+        <v>1899</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>174</v>
+        <v>2045</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>0.9252873563218391</v>
+        <v>0.9286063569682151</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1</v>
+        <v>2261</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2</v>
+        <v>2941</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7687861271676301</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>685</v>
+        <v>1635</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>732</v>
+        <v>1854</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>0.9357923497267759</v>
+        <v>0.8818770226537217</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.851063829787234</v>
+        <v>0.9047619047619048</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>47</v>
+        <v>2036</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>59</v>
+        <v>3192</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.6378446115288221</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1946</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>2062</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0.9437439379243453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>3</v>
+        <v>637</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>0</v>
+        <v>0.9843014128728415</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>1153</v>
+        <v>1049</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1437</v>
+        <v>1262</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0.802366040361865</v>
+        <v>0.8312202852614897</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.8837209302325582</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>100</v>
+        <v>1038</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.78</v>
+        <v>0.5183044315992292</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>3307</v>
+        <v>1246</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>3615</v>
+        <v>1377</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>0.9147994467496542</v>
+        <v>0.9048656499636892</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2197</v>
+        <v>1</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2305</v>
+        <v>1</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.9531453362255965</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>2764</v>
+        <v>5</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>3028</v>
+        <v>5</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0.9128137384412153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>1</v>
+        <v>1544</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2</v>
+        <v>1934</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7983453981385729</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>3774</v>
+        <v>1</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>4480</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>0.8424107142857142</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>2296</v>
+        <v>0</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2621</v>
+        <v>1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.876001526135063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>1281</v>
+        <v>526</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1484</v>
+        <v>538</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.8632075471698113</v>
+        <v>0.9776951672862454</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>1983</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>0.957046332046332</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>547</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>825</v>
-      </c>
-      <c r="F111" s="4" t="n">
-        <v>0.6630303030303031</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>2559</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>2814</v>
-      </c>
-      <c r="F112" s="4" t="n">
-        <v>0.9093816631130064</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>707</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>820</v>
-      </c>
-      <c r="F113" s="4" t="n">
-        <v>0.8621951219512195</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>2813</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>2938</v>
-      </c>
-      <c r="F114" s="4" t="n">
-        <v>0.9574540503744043</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>2215</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>2624</v>
-      </c>
-      <c r="F115" s="4" t="n">
-        <v>0.8441310975609756</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>1899</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>2045</v>
-      </c>
-      <c r="F116" s="4" t="n">
-        <v>0.9286063569682151</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>2261</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>2941</v>
-      </c>
-      <c r="F117" s="4" t="n">
-        <v>0.7687861271676301</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>1635</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>1854</v>
-      </c>
-      <c r="F118" s="4" t="n">
-        <v>0.8818770226537217</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Tarapacá</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F119" s="4" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Tarapacá</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>2036</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>3192</v>
-      </c>
-      <c r="F120" s="4" t="n">
-        <v>0.6378446115288221</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>627</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>637</v>
-      </c>
-      <c r="F122" s="4" t="n">
-        <v>0.9843014128728415</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>1049</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>1262</v>
-      </c>
-      <c r="F123" s="4" t="n">
-        <v>0.8312202852614897</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Isla de Pascua</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>0.8837209302325582</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>538</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>1038</v>
-      </c>
-      <c r="F125" s="4" t="n">
-        <v>0.5183044315992292</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>1246</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>1377</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>0.9048656499636892</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Cabildo</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F127" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F128" s="4" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F129" s="4" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F130" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>1332</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>0.8633633633633634</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>967</v>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>0.4105480868665977</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>1832</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>2056</v>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>0.8910505836575876</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Bulnes</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F136" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Chillán</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>1544</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>1934</v>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>0.7983453981385729</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F138" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F140" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>526</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>538</v>
-      </c>
-      <c r="F141" s="4" t="n">
-        <v>0.9776951672862454</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F142"/>
+  <autoFilter ref="A1:F109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5155,7 +4297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6435,13 +5577,13 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>760</v>
+        <v>215</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>826</v>
+        <v>248</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.9200968523002422</v>
+        <v>0.8669354838709677</v>
       </c>
     </row>
     <row r="42">
@@ -6466,13 +5608,13 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6483,48 +5625,48 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Oscar Hernández E.(Curacautín)</t>
+          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>2781</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1</v>
+        <v>3624</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0</v>
+        <v>0.7673841059602649</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lonquimay</t>
+          <t>Hospital Santa Filomena de Graneros</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -6540,22 +5682,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Purén</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
@@ -6571,425 +5713,425 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Dino Stagno M.(Traiguén)</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José de Victoria</t>
+          <t>Hospital de Nancagua</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>653</v>
+        <v>3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.3124042879019908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Hospital Familiar y Comunitario Carahue</t>
+          <t>Hospital Del Salvador de Peumo</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo González Galeno (Cunco)</t>
+          <t>Hospital de Pichidegua</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Galvarino</t>
+          <t>Hospital de Pichilemu</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abraham Godoy Peña (Lautaro)</t>
+          <t>Hospital Dr. Franco Ravera Zunino</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>72</v>
+        <v>1737</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>103</v>
+        <v>2125</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.6990291262135923</v>
+        <v>0.8174117647058824</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hospital Familiar y Comunitario de Loncoche</t>
+          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1</v>
+        <v>792</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>7</v>
+        <v>957</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.8275862068965517</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Hospital Intercultural de Nueva Imperial</t>
+          <t>Centro Comunitario de Salud Familiar Angostura</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.9570552147239264</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pitrufquén</t>
+          <t>Hospital San Juan de Dios de San Fernando</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>65</v>
+        <v>735</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>77</v>
+        <v>790</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0.8441558441558441</v>
+        <v>0.930379746835443</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Francisco de Pucón (D)</t>
+          <t>Hospital San Vicente de Tagua -Tagua</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
         <v>37</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.8809523809523809</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Arturo Hillerns Larrañaga (Saavedra)</t>
+          <t>Hospital de Santa Cruz</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>4</v>
+        <v>666</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>4</v>
+        <v>725</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1</v>
+        <v>0.9186206896551724</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2781</v>
+        <v>633</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>3624</v>
+        <v>679</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0.7673841059602649</v>
+        <v>0.9322533136966127</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Toltén</t>
+          <t>Hospital de Calbuco</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Vilcún</t>
+          <t>Hospital de Frutillar</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -7005,115 +6147,115 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Villarrica</t>
+          <t>Hospital de Futaleufú</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>868</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>906</v>
+        <v>3</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.9580573951434879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Hospital Santa Filomena de Graneros</t>
+          <t>Hospital de Puerto Montt</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0</v>
+        <v>2654</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2</v>
+        <v>2739</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>0</v>
+        <v>0.9689667761956918</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>Hospital Base San José de Osorno</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1</v>
+        <v>1255</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1</v>
+        <v>1443</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1</v>
+        <v>0.8697158697158697</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Hospital de Purranque Dr. Juan Hepp Dubiau</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -7129,2576 +6271,1553 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Nancagua</t>
+          <t>Hospital Juan Morey (La Unión)</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Hospital Del Salvador de Peumo</t>
+          <t>Hospital de Paillaco</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8421052631578947</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pichidegua</t>
+          <t>Hospital de Panguipulli</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7903225806451613</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pichilemu</t>
+          <t>Hospital de Río Bueno</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>0.7058823529411765</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Franco Ravera Zunino</t>
+          <t>Hospital Base Valdivia</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1737</v>
+        <v>723</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2125</v>
+        <v>994</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.8174117647058824</v>
+        <v>0.727364185110664</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
+          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>792</v>
+        <v>161</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>957</v>
+        <v>174</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.9252873563218391</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Angostura</t>
+          <t>Hospital Dr. Marco Antonio Chamorro ( Porvenir)</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios de San Fernando</t>
+          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>735</v>
+        <v>685</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>790</v>
+        <v>732</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>0.930379746835443</v>
+        <v>0.9357923497267759</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Vicente de Tagua -Tagua</t>
+          <t>Hospital San Juan de Dios (Cauquenes)</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.851063829787234</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Santa Cruz</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>666</v>
+        <v>47</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>725</v>
+        <v>59</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.9186206896551724</v>
+        <v>0.7966101694915254</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>Hospital San Juan de Dios (Curicó)</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>208</v>
+        <v>1946</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>238</v>
+        <v>2062</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.8739495798319328</v>
+        <v>0.9437439379243453</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>Hospital de Licantén</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>757</v>
+        <v>3</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.9220607661822986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>182</v>
+        <v>1153</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>199</v>
+        <v>1437</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.914572864321608</v>
+        <v>0.802366040361865</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Achao</t>
+          <t>Hospital San José (Parral)</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0</v>
+        <v>0.6574074074074074</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Calbuco</t>
+          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Frutillar</t>
+          <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1</v>
+        <v>3307</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1</v>
+        <v>3615</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1</v>
+        <v>0.9147994467496542</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Futaleufú</t>
+          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>3</v>
+        <v>2197</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>3</v>
+        <v>2305</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>1</v>
+        <v>0.9531453362255965</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Puerto Montt</t>
+          <t>Hospital Clínico San Borja Arriarán</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2654</v>
+        <v>2764</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2739</v>
+        <v>3028</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0.9689667761956918</v>
+        <v>0.9128137384412153</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Hospital Base San José de Osorno</t>
+          <t>SAPU Esmeralda</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>1255</v>
+        <v>1</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1443</v>
+        <v>1</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.8697158697158697</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Purranque Dr. Juan Hepp Dubiau</t>
+          <t>SAR Colina</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="G83" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Hospital Juan Morey (La Unión)</t>
+          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>64</v>
+        <v>3774</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>70</v>
+        <v>4480</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8424107142857142</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lanco</t>
+          <t>Hospital  Félix Bulnes Cerda</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1</v>
+        <v>2296</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2</v>
+        <v>2621</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.5</v>
+        <v>0.876001526135063</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Los Lagos</t>
+          <t>Hospital de Curacaví</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Hospital Santa Elisa de San José de la Mariquina</t>
+          <t>Hospital San José (Melipilla)</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>19</v>
+        <v>1281</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>20</v>
+        <v>1484</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.95</v>
+        <v>0.8632075471698113</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Paillaco</t>
+          <t>Hospital de Peñaflor</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8387096774193549</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Panguipulli</t>
+          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>49</v>
+        <v>1983</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>62</v>
+        <v>2072</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.957046332046332</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Río Bueno</t>
+          <t>Hospital Adalberto Steeger (Talagante)</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>12</v>
+        <v>547</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>17</v>
+        <v>825</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6630303030303031</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Hospital Base Valdivia</t>
+          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1119</v>
+        <v>2559</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1700</v>
+        <v>2814</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.658235294117647</v>
+        <v>0.9093816631130064</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
+          <t>Hospital El Pino (Santiago, San Bernardo)</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>161</v>
+        <v>1544</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>174</v>
+        <v>1629</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.9252873563218391</v>
+        <v>0.9478207489257213</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Marco Antonio Chamorro ( Porvenir)</t>
+          <t>Hospital Parroquial de San Bernardo (D)</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1</v>
+        <v>1269</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2</v>
+        <v>1309</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9694423223834988</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
+          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>685</v>
+        <v>1899</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>732</v>
+        <v>2045</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.9357923497267759</v>
+        <v>0.9286063569682151</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Cauquenes)</t>
+          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>160</v>
+        <v>2261</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>188</v>
+        <v>2941</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.851063829787234</v>
+        <v>0.7687861271676301</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>47</v>
+        <v>1635</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>59</v>
+        <v>1854</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.8818770226537217</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Curicó)</t>
+          <t>Centro de Salud Familiar Pedro Pulgar Melgarejo</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1946</v>
+        <v>7</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2062</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0.9437439379243453</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Licantén</t>
+          <t>Hospital de Alto Hospicio</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1153</v>
+        <v>2036</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1437</v>
+        <v>3192</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.802366040361865</v>
+        <v>0.6378446115288221</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Parral)</t>
+          <t>Hospital San Francisco (Llaillay)</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.6574074074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+          <t>Hospital San Juan de Dios (Los Andes)</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>78</v>
+        <v>627</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>100</v>
+        <v>637</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>0.78</v>
+        <v>0.9843014128728415</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
+          <t>Hospital San Camilo de San Felipe</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>3307</v>
+        <v>1049</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>3615</v>
+        <v>1262</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.9147994467496542</v>
+        <v>0.8312202852614897</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
+          <t>Hospital Hanga Roa (Isla De Pascua)</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2197</v>
+        <v>76</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>2305</v>
+        <v>86</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>0.9531453362255965</v>
+        <v>0.8837209302325582</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico San Borja Arriarán</t>
+          <t>Hospital Claudio Vicuña (San Antonio)</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2764</v>
+        <v>538</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>3028</v>
+        <v>1038</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.9128137384412153</v>
+        <v>0.5183044315992292</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>SAPU Esmeralda</t>
+          <t>Hospital Carlos Van Buren (Valparaíso)</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1</v>
+        <v>1246</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1</v>
+        <v>1377</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1</v>
+        <v>0.9048656499636892</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>SAR Colina</t>
+          <t>Hospital Adriana Cousiño (Quintero)</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>3774</v>
+        <v>5</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>4480</v>
+        <v>5</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0.8424107142857142</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Hospital  Félix Bulnes Cerda</t>
+          <t>Hospital Clínico Herminda Martín (Chillán)</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>2296</v>
+        <v>1544</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2621</v>
+        <v>1934</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.876001526135063</v>
+        <v>0.7983453981385729</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Curacaví</t>
+          <t>Hospital Comunitario de Salud Familiar Dr. Eduardo Contreras Trabucco de Coelemu</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Melipilla)</t>
+          <t>Hospital Comunitario de Salud Familiar de El Carmen</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1281</v>
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1484</v>
+        <v>1</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.8632075471698113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital de San Carlos</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1983</v>
+        <v>526</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>2072</v>
+        <v>538</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.957046332046332</v>
+        <v>0.9776951672862454</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Hospital Adalberto Steeger (Talagante)</t>
+          <t>Hospital Comunitario de Salud Familiar Pedro Morales Campos (Yungay)</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>825</v>
+        <v>1</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>0.6630303030303031</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>2559</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>2814</v>
-      </c>
-      <c r="G114" s="4" t="n">
-        <v>0.9093816631130064</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Hospital San Luis (Buin)</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>707</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>820</v>
-      </c>
-      <c r="G115" s="4" t="n">
-        <v>0.8621951219512195</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Hospital El Pino (Santiago, San Bernardo)</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>1629</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>0.9478207489257213</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Parroquial de San Bernardo (D)</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>1269</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>1309</v>
-      </c>
-      <c r="G117" s="4" t="n">
-        <v>0.9694423223834988</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Barros Luco Trudeau (Santiago, San Miguel)</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>2215</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>2624</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>0.8441310975609756</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>1899</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>2045</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>0.9286063569682151</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>2261</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>2941</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>0.7687861271676301</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>1635</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>1854</v>
-      </c>
-      <c r="G121" s="4" t="n">
-        <v>0.8818770226537217</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Tarapacá</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Centro de Salud Familiar Pedro Pulgar Melgarejo</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="4" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Tarapacá</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Hospital de Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Tarapacá</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>3192</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.6378446115288221</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Hospital San Francisco (Llaillay)</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Hospital San Juan de Dios (Los Andes)</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>627</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>637</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>0.9843014128728415</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Aconcagua</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Hospital San Camilo de San Felipe</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>1262</v>
-      </c>
-      <c r="G127" s="4" t="n">
-        <v>0.8312202852614897</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Isla de Pascua</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Hanga Roa (Isla De Pascua)</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>0.8837209302325582</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Claudio Vicuña (San Antonio)</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>538</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>1038</v>
-      </c>
-      <c r="G129" s="4" t="n">
-        <v>0.5183044315992292</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Carlos Van Buren (Valparaíso)</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>1246</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>1377</v>
-      </c>
-      <c r="G130" s="4" t="n">
-        <v>0.9048656499636892</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Cabildo</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Dr. Víctor Hugo Moll (Cabildo)</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Dr. Mario Sánchez Vergara (La Calera)</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Hospital San Agustín (La Ligua)</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G133" s="4" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Santo Tomás (Limache)</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Hospital de Petorca</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G135" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Biprovincial Quillota Petorca</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>1332</v>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>0.8633633633633634</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Hospital de Quilpué</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>967</v>
-      </c>
-      <c r="G137" s="4" t="n">
-        <v>0.4105480868665977</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Adriana Cousiño (Quintero)</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G138" s="4" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Dr. Gustavo Fricke (Viña del Mar)</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>1832</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>2056</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>0.8910505836575876</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Bulnes</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G140" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Chillán</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Clínico Herminda Martín (Chillán)</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>1934</v>
-      </c>
-      <c r="G141" s="4" t="n">
-        <v>0.7983453981385729</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Comunitario de Salud Familiar Dr. Eduardo Contreras Trabucco de Coelemu</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G142" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Comunitario de Salud Familiar de El Carmen</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G144" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Hospital de San Carlos</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>526</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>538</v>
-      </c>
-      <c r="G145" s="4" t="n">
-        <v>0.9776951672862454</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de Salud Ñuble</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Hospital Comunitario de Salud Familiar Pedro Morales Campos (Yungay)</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G146"/>
+  <autoFilter ref="A1:G113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>